--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2020_maule.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2020_maule.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>26.27796751934202</v>
+      </c>
+      <c r="C2">
         <v>28.9663344253154</v>
-      </c>
-      <c r="C2">
-        <v>26.27796751934202</v>
       </c>
       <c r="D2">
         <v>3.452283555512777</v>
       </c>
       <c r="E2">
-        <v>18.65854917859821</v>
+        <v>16.92684832240076</v>
       </c>
       <c r="F2">
         <v>64.41460249900102</v>
       </c>
       <c r="G2">
-        <v>16.92684832240076</v>
+        <v>18.65854917859821</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>28.14386397395784</v>
+      </c>
+      <c r="C3">
         <v>25.96314907872696</v>
-      </c>
-      <c r="C3">
-        <v>28.14386397395784</v>
       </c>
       <c r="D3">
         <v>3.851612903225806</v>
       </c>
       <c r="E3">
-        <v>16.84748056848711</v>
+        <v>18.26254588708189</v>
       </c>
       <c r="F3">
         <v>64.889973544431</v>
       </c>
       <c r="G3">
-        <v>18.26254588708189</v>
+        <v>16.84748056848711</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>25.61041779707</v>
+      </c>
+      <c r="C4">
         <v>48.25465726171097</v>
-      </c>
-      <c r="C4">
-        <v>25.61041779707</v>
       </c>
       <c r="D4">
         <v>2.072338830584707</v>
       </c>
       <c r="E4">
-        <v>27.75408301258712</v>
+        <v>14.73005305315718</v>
       </c>
       <c r="F4">
         <v>57.5158639342557</v>
       </c>
       <c r="G4">
-        <v>14.73005305315718</v>
+        <v>27.75408301258712</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>30.27444253859348</v>
+      </c>
+      <c r="C5">
         <v>32.71869639794168</v>
-      </c>
-      <c r="C5">
-        <v>30.27444253859348</v>
       </c>
       <c r="D5">
         <v>3.056356487549148</v>
       </c>
       <c r="E5">
+        <v>18.57405945803736</v>
+      </c>
+      <c r="F5">
+        <v>61.3522757169166</v>
+      </c>
+      <c r="G5">
         <v>20.07366482504604</v>
-      </c>
-      <c r="F5">
-        <v>61.35227571691659</v>
-      </c>
-      <c r="G5">
-        <v>18.57405945803736</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>36.18136020151134</v>
+      </c>
+      <c r="C6">
         <v>17.82367758186398</v>
-      </c>
-      <c r="C6">
-        <v>36.18136020151134</v>
       </c>
       <c r="D6">
         <v>5.610514414923686</v>
       </c>
       <c r="E6">
-        <v>11.57343801112201</v>
+        <v>23.49362119725221</v>
       </c>
       <c r="F6">
         <v>64.93294079162578</v>
       </c>
       <c r="G6">
-        <v>23.49362119725221</v>
+        <v>11.57343801112201</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>26.18216439225642</v>
+      </c>
+      <c r="C7">
         <v>36.05204696921612</v>
-      </c>
-      <c r="C7">
-        <v>26.18216439225642</v>
       </c>
       <c r="D7">
         <v>2.773767605633803</v>
       </c>
       <c r="E7">
-        <v>22.22222222222222</v>
+        <v>16.13849765258216</v>
       </c>
       <c r="F7">
         <v>61.63928012519562</v>
       </c>
       <c r="G7">
-        <v>16.13849765258216</v>
+        <v>22.22222222222222</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>20.64546016059296</v>
+      </c>
+      <c r="C8">
         <v>33.58554663372452</v>
-      </c>
-      <c r="C8">
-        <v>20.64546016059296</v>
       </c>
       <c r="D8">
         <v>2.977471264367816</v>
       </c>
       <c r="E8">
-        <v>21.77613135762916</v>
+        <v>13.38606327593112</v>
       </c>
       <c r="F8">
         <v>64.83780536643974</v>
       </c>
       <c r="G8">
-        <v>13.38606327593112</v>
+        <v>21.77613135762916</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>28.30544164911892</v>
+      </c>
+      <c r="C9">
         <v>32.8715504821013</v>
-      </c>
-      <c r="C9">
-        <v>28.30544164911892</v>
       </c>
       <c r="D9">
         <v>3.042144302090358</v>
       </c>
       <c r="E9">
+        <v>17.56171353915974</v>
+      </c>
+      <c r="F9">
+        <v>62.04359485663206</v>
+      </c>
+      <c r="G9">
         <v>20.39469160420821</v>
-      </c>
-      <c r="F9">
-        <v>62.04359485663205</v>
-      </c>
-      <c r="G9">
-        <v>17.56171353915973</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>29.87305859673371</v>
+      </c>
+      <c r="C10">
         <v>30.67326228494526</v>
-      </c>
-      <c r="C10">
-        <v>29.87305859673371</v>
       </c>
       <c r="D10">
         <v>3.260168386102217</v>
       </c>
       <c r="E10">
+        <v>18.60712748363126</v>
+      </c>
+      <c r="F10">
+        <v>62.28731960397835</v>
+      </c>
+      <c r="G10">
         <v>19.1055529123904</v>
-      </c>
-      <c r="F10">
-        <v>62.28731960397834</v>
-      </c>
-      <c r="G10">
-        <v>18.60712748363125</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>26.07949293542849</v>
+      </c>
+      <c r="C11">
         <v>30.48989832298957</v>
-      </c>
-      <c r="C11">
-        <v>26.07949293542849</v>
       </c>
       <c r="D11">
         <v>3.279774794283239</v>
       </c>
       <c r="E11">
-        <v>19.47372859913974</v>
+        <v>16.65682719068904</v>
       </c>
       <c r="F11">
-        <v>63.8694442101712</v>
+        <v>63.86944421017121</v>
       </c>
       <c r="G11">
-        <v>16.65682719068904</v>
+        <v>19.47372859913975</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>27.70339465200076</v>
+      </c>
+      <c r="C12">
         <v>37.78494215816423</v>
-      </c>
-      <c r="C12">
-        <v>27.70339465200076</v>
       </c>
       <c r="D12">
         <v>2.646556916281871</v>
       </c>
       <c r="E12">
-        <v>22.83238981458137</v>
+        <v>16.74039100639454</v>
       </c>
       <c r="F12">
         <v>60.42721917902409</v>
       </c>
       <c r="G12">
-        <v>16.74039100639454</v>
+        <v>22.83238981458137</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>27.15864394081289</v>
+      </c>
+      <c r="C13">
         <v>37.47892863832178</v>
-      </c>
-      <c r="C13">
-        <v>27.15864394081289</v>
       </c>
       <c r="D13">
         <v>2.668165917041479</v>
       </c>
       <c r="E13">
-        <v>22.76450511945393</v>
+        <v>16.49601820250285</v>
       </c>
       <c r="F13">
         <v>60.73947667804324</v>
       </c>
       <c r="G13">
-        <v>16.49601820250285</v>
+        <v>22.76450511945393</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>25.39620426531011</v>
+      </c>
+      <c r="C14">
         <v>40.07043631383291</v>
-      </c>
-      <c r="C14">
-        <v>25.39620426531011</v>
       </c>
       <c r="D14">
         <v>2.49560546875</v>
       </c>
       <c r="E14">
-        <v>24.21662528083245</v>
+        <v>15.3482322336526</v>
       </c>
       <c r="F14">
         <v>60.43514248551496</v>
       </c>
       <c r="G14">
-        <v>15.3482322336526</v>
+        <v>24.21662528083245</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>26.81592648734147</v>
+      </c>
+      <c r="C15">
         <v>25.41308502725655</v>
-      </c>
-      <c r="C15">
-        <v>26.81592648734147</v>
       </c>
       <c r="D15">
         <v>3.934980735032602</v>
       </c>
       <c r="E15">
-        <v>16.69398281865579</v>
+        <v>17.61551639896838</v>
       </c>
       <c r="F15">
         <v>65.69050078237582</v>
       </c>
       <c r="G15">
-        <v>17.61551639896838</v>
+        <v>16.69398281865579</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>24.75806451612903</v>
+      </c>
+      <c r="C16">
         <v>39.24193548387097</v>
-      </c>
-      <c r="C16">
-        <v>24.75806451612903</v>
       </c>
       <c r="D16">
         <v>2.548294286888615</v>
       </c>
       <c r="E16">
-        <v>23.92800944138473</v>
+        <v>15.0963808025177</v>
       </c>
       <c r="F16">
         <v>60.97560975609756</v>
       </c>
       <c r="G16">
-        <v>15.0963808025177</v>
+        <v>23.92800944138473</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>27.02445974827832</v>
+      </c>
+      <c r="C17">
         <v>35.62099263832819</v>
-      </c>
-      <c r="C17">
-        <v>27.02445974827832</v>
       </c>
       <c r="D17">
         <v>2.807333333333333</v>
       </c>
       <c r="E17">
-        <v>21.90100744634253</v>
+        <v>16.61556431595853</v>
       </c>
       <c r="F17">
         <v>61.48342823769893</v>
       </c>
       <c r="G17">
-        <v>16.61556431595853</v>
+        <v>21.90100744634253</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>28.28704174721063</v>
+      </c>
+      <c r="C18">
         <v>30.51514226608336</v>
-      </c>
-      <c r="C18">
-        <v>28.28704174721063</v>
       </c>
       <c r="D18">
         <v>3.277061569237608</v>
       </c>
       <c r="E18">
-        <v>19.21582027078973</v>
+        <v>17.81275359842822</v>
       </c>
       <c r="F18">
         <v>62.97142613078205</v>
       </c>
       <c r="G18">
-        <v>17.81275359842822</v>
+        <v>19.21582027078973</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>28.77675363224496</v>
+      </c>
+      <c r="C19">
         <v>33.08857990938916</v>
-      </c>
-      <c r="C19">
-        <v>28.77675363224496</v>
       </c>
       <c r="D19">
         <v>3.02219074598678</v>
       </c>
       <c r="E19">
-        <v>20.44204227391178</v>
+        <v>17.77820673680147</v>
       </c>
       <c r="F19">
         <v>61.77975098928675</v>
       </c>
       <c r="G19">
-        <v>17.77820673680147</v>
+        <v>20.44204227391179</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>26.4888500218627</v>
+      </c>
+      <c r="C20">
         <v>28.19414079580237</v>
-      </c>
-      <c r="C20">
-        <v>26.4888500218627</v>
       </c>
       <c r="D20">
         <v>3.546836228287841</v>
       </c>
       <c r="E20">
-        <v>18.22704658525554</v>
+        <v>17.12460425146993</v>
       </c>
       <c r="F20">
         <v>64.64834916327455</v>
       </c>
       <c r="G20">
-        <v>17.12460425146993</v>
+        <v>18.22704658525554</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>25.22025524907369</v>
+      </c>
+      <c r="C21">
         <v>30.62988884314532</v>
-      </c>
-      <c r="C21">
-        <v>25.22025524907369</v>
       </c>
       <c r="D21">
         <v>3.264784946236559</v>
       </c>
       <c r="E21">
-        <v>19.65342349957734</v>
+        <v>16.1823753169907</v>
       </c>
       <c r="F21">
         <v>64.16420118343196</v>
       </c>
       <c r="G21">
-        <v>16.1823753169907</v>
+        <v>19.65342349957734</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>26.5291684806269</v>
+      </c>
+      <c r="C22">
         <v>29.68001741401828</v>
-      </c>
-      <c r="C22">
-        <v>26.5291684806269</v>
       </c>
       <c r="D22">
         <v>3.369270260359369</v>
       </c>
       <c r="E22">
-        <v>19.00017418568194</v>
+        <v>16.98310398885211</v>
       </c>
       <c r="F22">
         <v>64.01672182546594</v>
       </c>
       <c r="G22">
-        <v>16.98310398885211</v>
+        <v>19.00017418568194</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>25.4996003197442</v>
+      </c>
+      <c r="C23">
         <v>38.76898481215028</v>
-      </c>
-      <c r="C23">
-        <v>25.4996003197442</v>
       </c>
       <c r="D23">
         <v>2.579381443298969</v>
       </c>
       <c r="E23">
-        <v>23.60097323600973</v>
+        <v>15.52311435523114</v>
       </c>
       <c r="F23">
         <v>60.87591240875912</v>
       </c>
       <c r="G23">
-        <v>15.52311435523114</v>
+        <v>23.60097323600973</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>26.55151950526283</v>
+      </c>
+      <c r="C24">
         <v>30.49629884124059</v>
-      </c>
-      <c r="C24">
-        <v>26.55151950526283</v>
       </c>
       <c r="D24">
         <v>3.279086439983613</v>
       </c>
       <c r="E24">
-        <v>19.41847977407422</v>
+        <v>16.90664651366294</v>
       </c>
       <c r="F24">
         <v>63.67487371226284</v>
       </c>
       <c r="G24">
-        <v>16.90664651366294</v>
+        <v>19.41847977407422</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>30.26699401565137</v>
+      </c>
+      <c r="C25">
         <v>31.72471996317324</v>
-      </c>
-      <c r="C25">
-        <v>30.26699401565137</v>
       </c>
       <c r="D25">
         <v>3.152116082224909</v>
       </c>
       <c r="E25">
-        <v>19.58416216728237</v>
+        <v>18.68428530832623</v>
       </c>
       <c r="F25">
         <v>61.7315525243914</v>
       </c>
       <c r="G25">
-        <v>18.68428530832623</v>
+        <v>19.58416216728237</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>27.58469466067317</v>
+      </c>
+      <c r="C26">
         <v>31.90987830281767</v>
-      </c>
-      <c r="C26">
-        <v>27.58469466067317</v>
       </c>
       <c r="D26">
         <v>3.13382580312661</v>
       </c>
       <c r="E26">
-        <v>20.00687403333906</v>
+        <v>17.29506788107922</v>
       </c>
       <c r="F26">
         <v>62.69805808558172</v>
       </c>
       <c r="G26">
-        <v>17.29506788107922</v>
+        <v>20.00687403333906</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>28.14451553580323</v>
+      </c>
+      <c r="C27">
         <v>34.05616643040496</v>
-      </c>
-      <c r="C27">
-        <v>28.14451553580323</v>
       </c>
       <c r="D27">
         <v>2.936325795927551</v>
       </c>
       <c r="E27">
-        <v>20.99631519274376</v>
+        <v>17.35166288737717</v>
       </c>
       <c r="F27">
         <v>61.65202191987905</v>
       </c>
       <c r="G27">
-        <v>17.35166288737717</v>
+        <v>20.99631519274376</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>28.66062264796442</v>
+      </c>
+      <c r="C28">
         <v>34.38248374957236</v>
-      </c>
-      <c r="C28">
-        <v>28.66062264796442</v>
       </c>
       <c r="D28">
         <v>2.908457711442786</v>
       </c>
       <c r="E28">
-        <v>21.08797146304359</v>
+        <v>17.57855531658186</v>
       </c>
       <c r="F28">
         <v>61.33347322037454</v>
       </c>
       <c r="G28">
-        <v>17.57855531658186</v>
+        <v>21.08797146304359</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>28.03578160880145</v>
+      </c>
+      <c r="C29">
         <v>31.34318127292045</v>
-      </c>
-      <c r="C29">
-        <v>28.03578160880145</v>
       </c>
       <c r="D29">
         <v>3.190486604702023</v>
       </c>
       <c r="E29">
-        <v>19.66582082491076</v>
+        <v>17.59064126274139</v>
       </c>
       <c r="F29">
         <v>62.74353791234786</v>
       </c>
       <c r="G29">
-        <v>17.59064126274139</v>
+        <v>19.66582082491076</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>27.97890680458372</v>
+      </c>
+      <c r="C30">
         <v>35.91927796369536</v>
-      </c>
-      <c r="C30">
-        <v>27.97890680458372</v>
       </c>
       <c r="D30">
         <v>2.784020327498588</v>
       </c>
       <c r="E30">
+        <v>17.07090706595719</v>
+      </c>
+      <c r="F30">
+        <v>61.0134884296498</v>
+      </c>
+      <c r="G30">
         <v>21.91560450439302</v>
-      </c>
-      <c r="F30">
-        <v>61.01348842964979</v>
-      </c>
-      <c r="G30">
-        <v>17.07090706595718</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>30.44923544496154</v>
+      </c>
+      <c r="C31">
         <v>30.03134200778802</v>
-      </c>
-      <c r="C31">
-        <v>30.44923544496154</v>
       </c>
       <c r="D31">
         <v>3.329854522454143</v>
       </c>
       <c r="E31">
-        <v>18.71338107356335</v>
+        <v>18.97378232822394</v>
       </c>
       <c r="F31">
         <v>62.31283659821269</v>
       </c>
       <c r="G31">
-        <v>18.97378232822394</v>
+        <v>18.71338107356335</v>
       </c>
     </row>
   </sheetData>
